--- a/data/2FEB_25_26/clutch_data_25_26_2FEB.xlsx
+++ b/data/2FEB_25_26/clutch_data_25_26_2FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1091"/>
+  <dimension ref="A1:Z1165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98660,6 +98660,6666 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1092" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>A. MORALES ROS</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="G1092" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="I1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1092" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="Y1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1092" t="n">
+        <v>38.07</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1093" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>D. ORRIT SERRANO</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="G1093" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="I1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1093" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1093" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1094" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>J. BERGENS</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="G1094" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>562.1999999999999</v>
+      </c>
+      <c r="I1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1094" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1094" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1094" t="n">
+        <v>4</v>
+      </c>
+      <c r="O1094" t="n">
+        <v>4</v>
+      </c>
+      <c r="P1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1094" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1094" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1094" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1094" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="Y1094" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1094" t="n">
+        <v>-5.06</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1095" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>J. CERA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="G1095" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>520.2</v>
+      </c>
+      <c r="I1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1095" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1095" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1095" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1095" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1095" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1095" t="n">
+        <v>3</v>
+      </c>
+      <c r="V1095" t="n">
+        <v>2</v>
+      </c>
+      <c r="W1095" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1095" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="Y1095" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z1095" t="n">
+        <v>35.11</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1096" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>N. OKEKE</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="G1096" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="I1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1096" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1096" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1096" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1096" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1096" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1096" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1096" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1096" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="Y1096" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1096" t="n">
+        <v>14.04</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1097" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>R. BLAK MOLLER</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="G1097" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="I1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1097" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1097" t="n">
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1098" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>R. HAYES</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="G1098" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>598.8000000000001</v>
+      </c>
+      <c r="I1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1098" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1098" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1098" t="n">
+        <v>4</v>
+      </c>
+      <c r="O1098" t="n">
+        <v>3</v>
+      </c>
+      <c r="P1098" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1098" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1098" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1098" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="Y1098" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1098" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1099" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>S. ROMERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="G1099" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="H1099" t="n">
+        <v>369</v>
+      </c>
+      <c r="I1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1099" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="Y1099" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1099" t="n">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1100" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>A. BIRD-JELINEK</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1100" t="n">
+        <v>108</v>
+      </c>
+      <c r="I1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1100" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1100" t="n">
+        <v>-38.89</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1101" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>A. INFANTE GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1101" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H1101" t="n">
+        <v>330</v>
+      </c>
+      <c r="I1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1101" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="Y1101" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1101" t="n">
+        <v>-10.58</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1102" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>A. PLITZUWEIT</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1102" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>309</v>
+      </c>
+      <c r="I1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1102" t="n">
+        <v>4</v>
+      </c>
+      <c r="O1102" t="n">
+        <v>4</v>
+      </c>
+      <c r="P1102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1102" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="Y1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1102" t="n">
+        <v>-31.86</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1103" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>B. AREVALO SAENZ</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1103" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="H1103" t="n">
+        <v>427.2</v>
+      </c>
+      <c r="I1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1103" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1103" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1103" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="Y1103" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1103" t="n">
+        <v>-34.63</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1104" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>I. MONTERO MECA</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1104" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H1104" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="I1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1104" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1104" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1104" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1104" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="Y1104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1104" t="n">
+        <v>-19.75</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1105" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>L. OBAJO BELTRAN</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1105" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H1105" t="n">
+        <v>85.19999999999999</v>
+      </c>
+      <c r="I1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1105" t="n">
+        <v>-62.77</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1106" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>P. SALL</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1106" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="H1106" t="n">
+        <v>598.8000000000001</v>
+      </c>
+      <c r="I1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1106" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1106" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1106" t="n">
+        <v>4</v>
+      </c>
+      <c r="O1106" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1106" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1106" t="n">
+        <v>2</v>
+      </c>
+      <c r="T1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1106" t="n">
+        <v>6</v>
+      </c>
+      <c r="V1106" t="n">
+        <v>4</v>
+      </c>
+      <c r="W1106" t="n">
+        <v>2</v>
+      </c>
+      <c r="X1106" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="Y1106" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1106" t="n">
+        <v>-19.6</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1107" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>P. SANTOS SPENCER</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1107" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1107" t="n">
+        <v>487.1999999999999</v>
+      </c>
+      <c r="I1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1107" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1107" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="Y1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1107" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1108" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7 vs CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>S. SERRATO BALLETBO</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="G1108" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H1108" t="n">
+        <v>259.2</v>
+      </c>
+      <c r="I1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1108" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z1108" t="n">
+        <v>-46.23</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1109" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>A. CALVO TORRES</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="G1109" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1109" t="n">
+        <v>42</v>
+      </c>
+      <c r="I1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1109" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1110" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>C. NKALOULOU MILANDOU</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="G1110" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H1110" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="I1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1110" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1110" t="n">
+        <v>2</v>
+      </c>
+      <c r="W1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1110" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="Y1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1110" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1111" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>F. SANTANA ROSALES</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="G1111" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H1111" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="I1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1111" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1111" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1112" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>J. KNOTEK</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="G1112" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H1112" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="I1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1112" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1112" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1112" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1112" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="Q1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1112" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1112" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="Y1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1112" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1113" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>J. LACUNZA ABECIA</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="G1113" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="H1113" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="I1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1113" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1113" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1113" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1113" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1113" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1113" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Y1113" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1113" t="n">
+        <v>18.01</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>P. YARNOZ LUMBRERAS</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="G1114" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H1114" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="I1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1114" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1114" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="Y1114" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1114" t="n">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1115" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="G1115" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H1115" t="n">
+        <v>192</v>
+      </c>
+      <c r="I1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1115" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1115" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1115" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="Y1115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1115" t="n">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>G. ARCOS GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="G1116" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H1116" t="n">
+        <v>255</v>
+      </c>
+      <c r="I1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1116" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1116" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1116" t="n">
+        <v>-35.84</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>I. DUKE TOUSSAINT</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="G1117" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H1117" t="n">
+        <v>177</v>
+      </c>
+      <c r="I1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1117" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1117" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1117" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1117" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1117" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1117" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1117" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y1117" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1117" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1118" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>J. MENENDEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="G1118" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H1118" t="n">
+        <v>279</v>
+      </c>
+      <c r="I1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1118" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1118" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1118" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1118" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1118" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1118" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1118" t="n">
+        <v>-8.25</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1119" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>M. OKAFOR AUGUSTIN</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="G1119" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H1119" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="I1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1119" t="n">
+        <v>-7.75</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1120" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>S. BARROS GARCIA</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="G1120" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H1120" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="I1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1120" t="n">
+        <v>2</v>
+      </c>
+      <c r="S1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1120" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1120" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z1120" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1121" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>S. FRANCO GARCIA</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="G1121" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H1121" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="I1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1121" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1121" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1121" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1121" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1121" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1121" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y1121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1121" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1122" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO vs CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>T. PIERRE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="G1122" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H1122" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="I1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1122" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1122" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y1122" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1122" t="n">
+        <v>-10.19</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1123" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>J. LAFUENTE VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="G1123" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H1123" t="n">
+        <v>87</v>
+      </c>
+      <c r="I1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1123" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1123" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1124" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>L. GARCIA MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="G1124" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H1124" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="I1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1124" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1124" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1124" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y1124" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1124" t="n">
+        <v>236.97</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1125" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>M. SERRANO ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="G1125" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H1125" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="I1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1125" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1125" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1125" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y1125" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1125" t="n">
+        <v>236.97</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1126" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>S. KOCIC</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="G1126" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H1126" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="I1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1126" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1126" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1126" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="Y1126" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z1126" t="n">
+        <v>148.45</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1127" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>S. MENDIOLA DIEZ</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="G1127" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H1127" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1128" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>V. MORENO MARTIN</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="G1128" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H1128" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="I1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1128" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1128" t="n">
+        <v>236.97</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1129" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>V. STEVANIC</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="G1129" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H1129" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="I1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1129" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z1129" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1130" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>C. JACOBS</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="G1130" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H1130" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="I1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1130" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1130" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1130" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="Y1130" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1130" t="n">
+        <v>-236.97</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1131" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>E. A NONGO BERTHOLD</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="G1131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H1131" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1131" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1131" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1131" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="Y1131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1132" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>H. ARBOSA ROLDAN</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="G1132" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H1132" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="I1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1132" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1132" t="n">
+        <v>-236.97</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1133" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>J. PARDINA MOLINA</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="G1133" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="I1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1133" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1133" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1134" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>K. TORRES CUEVAS</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="G1134" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H1134" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="I1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1134" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1134" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="Y1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1134" t="n">
+        <v>-93.62</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>M. DE PABLO DEL CASTILLO</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="G1135" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H1135" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="I1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1135" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z1135" t="n">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>P. DIENE</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="G1136" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H1136" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="I1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1136" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1136" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="Y1136" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1136" t="n">
+        <v>-130.56</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO vs CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>R. UKAWUBA</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="G1137" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H1137" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="I1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1137" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1137" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="Y1137" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1137" t="n">
+        <v>-236.97</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>C. FIELDS</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="G1138" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H1138" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="I1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1138" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1138" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1138" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1138" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="Y1138" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1138" t="n">
+        <v>-57.53</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>G. BOAHEN</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="G1139" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H1139" t="n">
+        <v>129</v>
+      </c>
+      <c r="I1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1139" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1139" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1139" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1139" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y1139" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z1139" t="n">
+        <v>-127.27</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>G. VERGARA HARBOE</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="G1140" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H1140" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="I1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1140" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1140" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1140" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1140" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y1140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1140" t="n">
+        <v>-30.56</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>J. MARTINEZ MEGIAS</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="G1141" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H1141" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="I1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1141" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1141" t="n">
+        <v>2</v>
+      </c>
+      <c r="W1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1141" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1141" t="n">
+        <v>-57.53</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>J. SANTA BARBARA CARCELEN</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="G1142" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H1142" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="I1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1142" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1142" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="Y1142" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1142" t="n">
+        <v>-36.62</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>L. FAIAL</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="G1143" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H1143" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="I1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1143" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="Y1143" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z1143" t="n">
+        <v>-57.53</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>I. HANEY</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="G1144" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="I1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1144" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1144" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1144" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="Y1144" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1144" t="n">
+        <v>57.53</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1145" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>I. ORDOÑEZ OCHOA</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="G1145" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H1145" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="I1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1145" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1145" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1145" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="Y1145" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1145" t="n">
+        <v>57.53</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1146" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="G1146" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="I1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1146" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="Y1146" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1146" t="n">
+        <v>36.62</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1147" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>M. OCHI</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="G1147" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="I1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1147" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1147" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1147" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1147" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="Y1147" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1147" t="n">
+        <v>57.53</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1148" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>P. ISERN MAZA</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="G1148" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="I1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1148" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1148" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1148" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y1148" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1148" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1149" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID vs JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>P. MARIN FONTAN</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="G1149" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="I1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1149" t="n">
+        <v>4</v>
+      </c>
+      <c r="O1149" t="n">
+        <v>4</v>
+      </c>
+      <c r="P1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1149" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="Y1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1149" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1150" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>I. AIZPITARTE ARANZA</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1150" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>261</v>
+      </c>
+      <c r="I1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1150" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1150" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1150" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y1150" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1150" t="n">
+        <v>15.08</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1151" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>I. MIRANDA GARCIA</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1151" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>9</v>
+      </c>
+      <c r="I1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1152" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>J. CEBOLLA HERRERA</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1152" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="I1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1152" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z1152" t="n">
+        <v>-568.1799999999999</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1153" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>M. NIANG NDONGO</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1153" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>237</v>
+      </c>
+      <c r="I1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1153" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1153" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1153" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1153" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z1153" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1154" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>M. OLAIZOLA GARIN</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1154" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="I1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1154" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z1154" t="n">
+        <v>-568.1799999999999</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1155" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>N. WILLIAMS</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1155" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="I1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1155" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1155" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1155" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="Y1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1155" t="n">
+        <v>13.27</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1156" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>O. ARDANZA BERNAOLA</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1156" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="I1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1156" t="n">
+        <v>1</v>
+      </c>
+      <c r="T1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1156" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1157" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>O. INDA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1157" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>237</v>
+      </c>
+      <c r="I1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1157" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1157" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y1157" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z1157" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1158" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>T. SAGNA</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="G1158" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="I1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1158" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="Y1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1158" t="n">
+        <v>13.27</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1159" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>A. LATORRE SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="G1159" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="I1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1159" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1159" t="n">
+        <v>199.29</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1160" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>A. MOODY</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="G1160" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="I1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1160" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1160" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1160" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1160" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1160" t="n">
+        <v>2</v>
+      </c>
+      <c r="O1160" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1160" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1160" t="n">
+        <v>1</v>
+      </c>
+      <c r="V1160" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1160" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y1160" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1160" t="n">
+        <v>106.94</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1161" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>G. CLARKE</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="G1161" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="I1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1161" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="Y1161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1161" t="n">
+        <v>-13.27</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1162" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>J. FRANCH DE PABLO</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="G1162" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="I1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1162" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1162" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1162" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1162" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y1162" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z1162" t="n">
+        <v>-58.33</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1163" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>M. JANKOVIC</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="G1163" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>250.2</v>
+      </c>
+      <c r="I1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1163" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1163" t="n">
+        <v>2</v>
+      </c>
+      <c r="V1163" t="n">
+        <v>2</v>
+      </c>
+      <c r="W1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1163" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z1163" t="n">
+        <v>24.92</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1164" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>S. CECILIA PEREZ</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="G1164" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>270</v>
+      </c>
+      <c r="I1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z1164" t="n">
+        <v>-49.93</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="C1165" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>BIELE ISB vs INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>W. CABRAL BUERIBERI</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="G1165" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>237</v>
+      </c>
+      <c r="I1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1165" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1165" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z1165" t="n">
+        <v>-175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
